--- a/2_Formulas_Functions/3_Logical_Functions.xlsx
+++ b/2_Formulas_Functions/3_Logical_Functions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Mac\Home\Developer\_Courses\Excel\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kaiyuan Gao\Desktop\TGC-Code-Base\Excel_Data_Analytics_Course\2_Formulas_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DACF0C-E6D1-403B-A48D-03B483E33508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17BD0A3-49C9-4A4C-9B5E-4D95F7ABBAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-102" yWindow="1488" windowWidth="18372" windowHeight="10296" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
+    <workbookView xWindow="15045" yWindow="0" windowWidth="23460" windowHeight="20985" activeTab="2" xr2:uid="{8CC555B5-3E06-43B6-9E5B-C0A1D3498DA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Data_1" sheetId="7" r:id="rId1"/>
@@ -509,7 +509,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -559,6 +559,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -866,7 +872,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -959,6 +965,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1297,6 +1306,9 @@
   <wetp:taskpane dockstate="right" visibility="0" width="875" row="7">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
+  <wetp:taskpane dockstate="right" visibility="0" width="672" row="6">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </wetp:taskpane>
 </wetp:taskpanes>
 </file>
 
@@ -1317,35 +1329,49 @@
 </we:webextension>
 </file>
 
+<file path=xl/webextensions/webextension2.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{2818355F-E92F-4C63-80BA-A338CB9493D2}">
+  <we:reference id="wa200003696" version="1.3.0.0" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200003696" version="1.3.0.0" store="WA200003696" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="projectV0_1-56c6e055-265e-4713-816e-a646dbb708de" value="{&quot;kind&quot;:&quot;AFEJSONBlobNode&quot;,&quot;id&quot;:&quot;{AB6C4455-1136-41D6-BA6A-EA0154EF6A38}&quot;}"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D423364-12D3-4C3A-8A6B-C3645EBFE927}">
   <dimension ref="B1:Q16"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.15625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.68359375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26171875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26171875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.578125" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="11.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.26171875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="9.15625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="10.41796875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="9.68359375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.15625" style="1"/>
-    <col min="18" max="18" width="14.15625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15625" style="1"/>
+    <col min="1" max="1" width="5.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="11.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" style="1"/>
+    <col min="18" max="18" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G1" s="25"/>
     </row>
-    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1395,7 +1421,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
@@ -1452,9 +1478,12 @@
         <f>AND(L3,M3)</f>
         <v>1</v>
       </c>
-      <c r="Q3" s="32"/>
-    </row>
-    <row r="4" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q3" s="32" t="str">
+        <f>IF(P3,"GOAL MET", "NOT MET")</f>
+        <v>GOAL MET</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1511,9 +1540,12 @@
         <f t="shared" ref="P4:P12" si="10">AND(L4,M4)</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="32"/>
-    </row>
-    <row r="5" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q4" s="32" t="str">
+        <f t="shared" ref="Q4:Q12" si="11">IF(P4,"GOAL MET", "NOT MET")</f>
+        <v>NOT MET</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
@@ -1570,9 +1602,12 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q5" s="32"/>
-    </row>
-    <row r="6" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q5" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>NOT MET</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -1629,9 +1664,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q6" s="32"/>
-    </row>
-    <row r="7" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q6" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>GOAL MET</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
@@ -1688,9 +1726,12 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="32"/>
-    </row>
-    <row r="8" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q7" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>NOT MET</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
@@ -1747,9 +1788,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q8" s="32"/>
-    </row>
-    <row r="9" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q8" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>GOAL MET</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
@@ -1806,9 +1850,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q9" s="32"/>
-    </row>
-    <row r="10" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q9" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>GOAL MET</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
@@ -1865,9 +1912,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q10" s="32"/>
-    </row>
-    <row r="11" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q10" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>GOAL MET</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -1924,9 +1974,12 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="32"/>
-    </row>
-    <row r="12" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q11" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>NOT MET</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
         <v>9</v>
       </c>
@@ -1983,14 +2036,17 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="Q12" s="33"/>
-    </row>
-    <row r="14" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="Q12" s="32" t="str">
+        <f t="shared" si="11"/>
+        <v>GOAL MET</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="s">
         <v>22</v>
       </c>
@@ -1998,7 +2054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="15" t="s">
         <v>23</v>
       </c>
@@ -2014,33 +2070,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C913A13C-1EE0-4C25-B641-D7D4D62C7E1E}">
   <dimension ref="B1:Q16"/>
-  <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.15625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22.68359375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.41796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26171875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.578125" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="9.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="11.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.26171875" style="1" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="9.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10.41796875" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.15625" style="1" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="9.68359375" style="1" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="9.68359375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.15625" style="1"/>
-    <col min="19" max="19" width="14.15625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.15625" style="1"/>
+    <col min="1" max="1" width="5.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="11.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="1"/>
+    <col min="19" max="19" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G1" s="25"/>
     </row>
-    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:17" s="11" customFormat="1" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2090,7 +2146,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
@@ -2152,7 +2208,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
@@ -2214,7 +2270,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
@@ -2276,7 +2332,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
@@ -2338,7 +2394,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="7" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
@@ -2400,7 +2456,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="8" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
@@ -2462,7 +2518,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="9" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
@@ -2524,7 +2580,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="10" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
@@ -2586,7 +2642,7 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="11" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -2648,7 +2704,7 @@
         <v>Not Met</v>
       </c>
     </row>
-    <row r="12" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="8" t="s">
         <v>9</v>
       </c>
@@ -2710,12 +2766,12 @@
         <v>Goal Met</v>
       </c>
     </row>
-    <row r="14" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="13" t="s">
         <v>22</v>
       </c>
@@ -2723,7 +2779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:17" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="15" t="s">
         <v>23</v>
       </c>
@@ -2739,29 +2795,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B18E6D21-2229-4383-8B9A-431F68FAE08C}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.83984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.15625" customWidth="1"/>
-    <col min="3" max="3" width="21.83984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.15625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.15625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="68.15625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.9453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.26171875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.41796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.5234375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.3125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.41796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.68359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.05078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="38.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="19" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="68.140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="18.85546875" customWidth="1"/>
+    <col min="12" max="12" width="18.7109375" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
         <v>46</v>
       </c>
@@ -2817,7 +2873,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>56</v>
       </c>
@@ -2848,8 +2904,16 @@
       <c r="J2" s="27" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K2" t="str">
+        <f>IF(A2=K$1,"ROLE DESIRED", "NOT DESIRED")</f>
+        <v>NOT DESIRED</v>
+      </c>
+      <c r="L2" s="48" t="str">
+        <f>IF(A2=L1, "Desired","Not Desired")</f>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -2880,8 +2944,16 @@
       <c r="J3" s="27" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K3" t="str">
+        <f t="shared" ref="K3:K21" si="0">IF(A3=K$1,"ROLE DESIRED", "NOT DESIRED")</f>
+        <v>ROLE DESIRED</v>
+      </c>
+      <c r="L3" s="48" t="str">
+        <f t="shared" ref="L3:L21" si="1">IF(A3=L2, "Desired","Not Desired")</f>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
@@ -2910,8 +2982,16 @@
       <c r="J4" s="27" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K4" t="str">
+        <f t="shared" si="0"/>
+        <v>ROLE DESIRED</v>
+      </c>
+      <c r="L4" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
         <v>0</v>
       </c>
@@ -2940,8 +3020,16 @@
       <c r="J5" s="27" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K5" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT DESIRED</v>
+      </c>
+      <c r="L5" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
         <v>76</v>
       </c>
@@ -2970,8 +3058,16 @@
       <c r="J6" s="27" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K6" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT DESIRED</v>
+      </c>
+      <c r="L6" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
         <v>0</v>
       </c>
@@ -3000,8 +3096,16 @@
       <c r="J7" s="27" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K7" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT DESIRED</v>
+      </c>
+      <c r="L7" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
         <v>2</v>
       </c>
@@ -3030,8 +3134,16 @@
       <c r="J8" s="27" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K8" t="str">
+        <f t="shared" si="0"/>
+        <v>ROLE DESIRED</v>
+      </c>
+      <c r="L8" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
         <v>2</v>
       </c>
@@ -3062,8 +3174,16 @@
       <c r="J9" s="27" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K9" t="str">
+        <f t="shared" si="0"/>
+        <v>ROLE DESIRED</v>
+      </c>
+      <c r="L9" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
         <v>2</v>
       </c>
@@ -3092,8 +3212,16 @@
       <c r="J10" s="27" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K10" t="str">
+        <f t="shared" si="0"/>
+        <v>ROLE DESIRED</v>
+      </c>
+      <c r="L10" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
         <v>2</v>
       </c>
@@ -3124,8 +3252,16 @@
       <c r="J11" s="27" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K11" t="str">
+        <f t="shared" si="0"/>
+        <v>ROLE DESIRED</v>
+      </c>
+      <c r="L11" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
         <v>0</v>
       </c>
@@ -3156,8 +3292,16 @@
       <c r="J12" s="27" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K12" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT DESIRED</v>
+      </c>
+      <c r="L12" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
         <v>102</v>
       </c>
@@ -3188,8 +3332,16 @@
       <c r="J13" s="27" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K13" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT DESIRED</v>
+      </c>
+      <c r="L13" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="27" t="s">
         <v>0</v>
       </c>
@@ -3220,8 +3372,16 @@
       <c r="J14" s="27" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K14" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT DESIRED</v>
+      </c>
+      <c r="L14" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
         <v>0</v>
       </c>
@@ -3252,8 +3412,16 @@
       <c r="J15" s="27" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="K15" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT DESIRED</v>
+      </c>
+      <c r="L15" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="27" t="s">
         <v>4</v>
       </c>
@@ -3284,8 +3452,16 @@
       <c r="J16" s="27" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K16" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT DESIRED</v>
+      </c>
+      <c r="L16" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
         <v>4</v>
       </c>
@@ -3316,8 +3492,16 @@
       <c r="J17" s="27" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K17" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT DESIRED</v>
+      </c>
+      <c r="L17" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
         <v>123</v>
       </c>
@@ -3346,8 +3530,16 @@
       <c r="J18" s="27" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K18" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT DESIRED</v>
+      </c>
+      <c r="L18" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
         <v>0</v>
       </c>
@@ -3378,8 +3570,16 @@
       <c r="J19" s="27" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K19" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT DESIRED</v>
+      </c>
+      <c r="L19" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
@@ -3408,8 +3608,16 @@
       <c r="J20" s="27" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="K20" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT DESIRED</v>
+      </c>
+      <c r="L20" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
         <v>123</v>
       </c>
@@ -3440,38 +3648,47 @@
       <c r="J21" s="27" t="s">
         <v>135</v>
       </c>
+      <c r="K21" t="str">
+        <f t="shared" si="0"/>
+        <v>NOT DESIRED</v>
+      </c>
+      <c r="L21" s="48" t="str">
+        <f t="shared" si="1"/>
+        <v>Not Desired</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4064259-8981-41EE-A951-64D7FCDC9F77}">
   <dimension ref="A1:XFD21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.83984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.41796875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="21.83984375" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="11.15625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="38.15625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.578125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="18.578125" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="13.83984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="38.140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="68.15625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="15.83984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.15625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.26171875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.26171875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.15625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.26171875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.68359375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.41796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="68.140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
         <v>46</v>
       </c>
@@ -3531,7 +3748,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="2" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>56</v>
       </c>
@@ -3595,7 +3812,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="3" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -3659,7 +3876,7 @@
         <v>Salary Low</v>
       </c>
     </row>
-    <row r="4" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
@@ -3721,7 +3938,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="5" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
         <v>0</v>
       </c>
@@ -3783,7 +4000,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="6" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
         <v>76</v>
       </c>
@@ -3845,7 +4062,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="7" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
         <v>0</v>
       </c>
@@ -3907,7 +4124,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="8" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
         <v>2</v>
       </c>
@@ -3969,7 +4186,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="9" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
         <v>2</v>
       </c>
@@ -4033,7 +4250,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="10" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
         <v>2</v>
       </c>
@@ -4095,7 +4312,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="11" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
         <v>2</v>
       </c>
@@ -4159,7 +4376,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="12" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
         <v>0</v>
       </c>
@@ -4223,7 +4440,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="13" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
         <v>102</v>
       </c>
@@ -4287,7 +4504,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="14" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A14" s="27" t="s">
         <v>0</v>
       </c>
@@ -4351,7 +4568,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="15" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
         <v>0</v>
       </c>
@@ -4415,7 +4632,7 @@
         <v>Salary Low</v>
       </c>
     </row>
-    <row r="16" spans="1:18 16384:16384" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:18 16384:16384" x14ac:dyDescent="0.25">
       <c r="A16" s="27" t="s">
         <v>4</v>
       </c>
@@ -4479,7 +4696,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
         <v>4</v>
       </c>
@@ -4543,7 +4760,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
         <v>123</v>
       </c>
@@ -4605,7 +4822,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
         <v>0</v>
       </c>
@@ -4669,7 +4886,7 @@
         <v>Salary &gt; 85K</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="27" t="s">
         <v>0</v>
       </c>
@@ -4731,7 +4948,7 @@
         <v>No Data</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
         <v>123</v>
       </c>
@@ -4804,17 +5021,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08EBE098-CD97-45AE-AE7E-86DF2D94E426}">
   <dimension ref="B2:F9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.578125" customWidth="1"/>
-    <col min="2" max="2" width="13.41796875" customWidth="1"/>
-    <col min="3" max="3" width="31.41796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60.41796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.68359375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="26" t="s">
         <v>28</v>
       </c>
@@ -4831,7 +5048,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="e">
         <f>1/0</f>
         <v>#DIV/0!</v>
@@ -4851,7 +5068,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="e">
         <f>A4 + "text"</f>
         <v>#VALUE!</v>
@@ -4871,7 +5088,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
@@ -4891,7 +5108,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="e" cm="1">
         <f t="array" aca="1" ref="B6" ca="1">COUNTT(A3:A9)</f>
         <v>#NAME?</v>
@@ -4911,7 +5128,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="27" t="e">
         <f>VLOOKUP("Value", A1:A10, 2, FALSE)</f>
         <v>#N/A</v>
@@ -4931,7 +5148,7 @@
         <v>This hides #N/A error</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="27" t="e">
         <f>SQRT(-1)</f>
         <v>#NUM!</v>
@@ -4951,7 +5168,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="27" t="e">
         <f>SUM(A1:A10 C1:C10)</f>
         <v>#NULL!</v>
@@ -4979,14 +5196,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B83CC08-3BAC-45FD-A105-07186D54808A}">
   <dimension ref="B1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.83984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.578125" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="14.7" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>137</v>
       </c>
@@ -5000,7 +5217,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="38" t="b">
         <v>1</v>
       </c>
@@ -5016,7 +5233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="38" t="b">
         <v>1</v>
       </c>
@@ -5032,7 +5249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="38" t="b">
         <v>0</v>
       </c>
@@ -5048,7 +5265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="40" t="b">
         <v>0</v>
       </c>
@@ -5067,4 +5284,16 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAE0ARABZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB6C4455-1136-41D6-BA6A-EA0154EF6A38}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>